--- a/Convert_from_xlsx_to_Json/table_normalization/environment-table37.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/environment-table37.xlsx
@@ -100,7 +100,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="0.00000"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -339,16 +339,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -370,7 +367,7 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
@@ -386,28 +383,34 @@
     <xf numFmtId="2" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -916,530 +919,530 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="19"/>
-      <c r="B1" s="21" t="s">
+      <c r="A1" s="23"/>
+      <c r="B1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="21" t="s">
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="23"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="21"/>
     </row>
     <row r="2" spans="1:16" ht="39.5">
-      <c r="A2" s="20"/>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="24"/>
+      <c r="B2" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="25" t="s">
+      <c r="K2" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="M2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="15" t="s">
+      <c r="P2" s="14" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>3.63</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="6">
         <v>73.75</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="6">
         <v>21.89</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="6">
         <v>0.73</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="6">
         <v>0.18</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="6">
         <v>50.55</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="6">
         <v>5.71</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3" s="6">
         <v>0.15</v>
       </c>
-      <c r="J3" s="7">
+      <c r="J3" s="6">
         <v>39.049999999999997</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="5">
         <v>8863</v>
       </c>
-      <c r="L3" s="7">
+      <c r="L3" s="6">
         <v>5.56</v>
       </c>
-      <c r="M3" s="7">
+      <c r="M3" s="6">
         <v>35.93</v>
       </c>
-      <c r="N3" s="7">
+      <c r="N3" s="6">
         <v>33.229999999999997</v>
       </c>
-      <c r="O3" s="7">
+      <c r="O3" s="6">
         <v>16.53</v>
       </c>
-      <c r="P3" s="16">
+      <c r="P3" s="15">
         <v>8.75</v>
       </c>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="8">
         <v>6.49</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="8">
         <v>23.23</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="8">
         <v>64.28</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="8">
         <v>6</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="8">
         <v>0.02</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="8">
         <v>72.67</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="8">
         <v>3.65</v>
       </c>
-      <c r="I4" s="9">
+      <c r="I4" s="8">
         <v>0.48</v>
       </c>
-      <c r="J4" s="9">
+      <c r="J4" s="8">
         <v>10.69</v>
       </c>
-      <c r="K4" s="8">
+      <c r="K4" s="7">
         <v>12124</v>
       </c>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="17"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="16"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="8">
         <v>3.14</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="8">
         <v>48.34</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="8">
         <v>45.88</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="8">
         <v>2.64</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="8">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="8">
         <v>65.06</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="8">
         <v>4.78</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="8">
         <v>0.76</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="8">
         <v>23.55</v>
       </c>
-      <c r="K5" s="8">
+      <c r="K5" s="7">
         <v>11075</v>
       </c>
-      <c r="L5" s="9">
+      <c r="L5" s="8">
         <v>2.41</v>
       </c>
-      <c r="M5" s="9">
+      <c r="M5" s="8">
         <v>18.77</v>
       </c>
-      <c r="N5" s="9">
+      <c r="N5" s="8">
         <v>21.32</v>
       </c>
-      <c r="O5" s="9">
+      <c r="O5" s="8">
         <v>36.36</v>
       </c>
-      <c r="P5" s="17">
+      <c r="P5" s="16">
         <v>21.14</v>
       </c>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="8">
         <v>1.58</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="8">
         <v>64.11</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="8">
         <v>32.67</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="8">
         <v>1.64</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="8">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="8">
         <v>60.56</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="8">
         <v>5.4</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="8">
         <v>0.56000000000000005</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="8">
         <v>30.19</v>
       </c>
-      <c r="K6" s="8">
+      <c r="K6" s="7">
         <v>11055</v>
       </c>
-      <c r="L6" s="9">
+      <c r="L6" s="8">
         <v>21.98</v>
       </c>
-      <c r="M6" s="9">
+      <c r="M6" s="8">
         <v>38.6</v>
       </c>
-      <c r="N6" s="9">
+      <c r="N6" s="8">
         <v>18.71</v>
       </c>
-      <c r="O6" s="9">
+      <c r="O6" s="8">
         <v>17.71</v>
       </c>
-      <c r="P6" s="17">
+      <c r="P6" s="16">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="8">
         <v>0.92</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="8">
         <v>35.92</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="8">
         <v>49.72</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="8">
         <v>13.44</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="8">
         <v>1.69</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="8">
         <v>70.5</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="8">
         <v>4.9400000000000004</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="8">
         <v>1.46</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="8">
         <v>7.05</v>
       </c>
-      <c r="K7" s="8">
+      <c r="K7" s="7">
         <v>12841</v>
       </c>
-      <c r="L7" s="9">
+      <c r="L7" s="8">
         <v>0.16</v>
       </c>
-      <c r="M7" s="9">
+      <c r="M7" s="8">
         <v>3.09</v>
       </c>
-      <c r="N7" s="9">
+      <c r="N7" s="8">
         <v>22.48</v>
       </c>
-      <c r="O7" s="9">
+      <c r="O7" s="8">
         <v>30.46</v>
       </c>
-      <c r="P7" s="17">
+      <c r="P7" s="16">
         <v>43.81</v>
       </c>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="11"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
+      <c r="A8" s="10"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="11"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
+      <c r="A9" s="10"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="11"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
+      <c r="A10" s="10"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="11"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
+      <c r="A11" s="10"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="11"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
+      <c r="A12" s="10"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="11"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
+      <c r="A13" s="10"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" s="11"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
+      <c r="A14" s="10"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="11"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
+      <c r="A15" s="10"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="11"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
+      <c r="A16" s="10"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="11"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
+      <c r="A17" s="10"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="11"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
+      <c r="A18" s="10"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="11"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
+      <c r="A19" s="10"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="11"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
+      <c r="A20" s="10"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="11"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
+      <c r="A21" s="10"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="11"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
+      <c r="A22" s="10"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="11"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
+      <c r="A23" s="10"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="11"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
+      <c r="A24" s="10"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="11"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
+      <c r="A25" s="10"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="11"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
+      <c r="A26" s="10"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="11"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
+      <c r="A27" s="10"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="11"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
+      <c r="A28" s="10"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="11"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
+      <c r="A29" s="10"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
+      <c r="A30" s="12"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
+      <c r="A31" s="22"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="4">
